--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_BD.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_BD.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R5ff824fef6454b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rbcf5c0b836c04ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Rca35536fa03844e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rf17979b4b1404295"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Re92b39a73b89488f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Ra2982e3bc1ba4ec6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R1974784b42f74322"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R783a2f124cd14aa5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R131dbbbcb1ce42e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="Rd62b92e1abaf41fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R9f8b7ec4820f4b33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rff8c98af3bc44d54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R173394ea7c994740"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Re15e42604ad1495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R2e41f8fb45e34052"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R465488b6fd734efd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Ra34c7b96b4134130"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Ra685badff41a4837"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R0db1906d774a4605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R7b5a72c6b66a4d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rb923993d9e9142a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rd15dc68f20dd4443"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Rd55b143e12654c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R48489b519cb342ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R4d2c1e1d53084725"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R42c12086c7ed48ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R360d18b4a96c4edf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rbb71566749e3408a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rad371fdc9be84f35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R2c3b2c49785041e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R78a9954101674632"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R9473dd0752244800"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R17b49137e2684b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R2c13109bff294148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Ra374611adec14c3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R755fc490cbb04dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Rfd0a069670f44471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R4cc6a6d89b2144ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R38ac6429eaaf4488"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R0fb09ed8818f49f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R8b46ccba7bac4fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Ra7a433f1399f4eb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R2c7d35d8a83b440a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3895,6 +3896,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>タムドク</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>朝の国・ハンジ村</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
